--- a/appium-tests/appium_test_report.xlsx
+++ b/appium-tests/appium_test_report.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,12 +56,6 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00C62828"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
@@ -77,20 +71,8 @@
       <color rgb="00555555"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00721C24"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00721C24"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -100,25 +82,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E9ECEF"/>
-        <bgColor rgb="00E9ECEF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -162,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -177,13 +150,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -192,19 +162,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -572,31 +536,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SkillSphereAI Mobile E2E Test Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="10" customHeight="1"/>
-    <row r="3" ht="25" customHeight="1">
+          <t>SkillSphereAI — Appium Mobile E2E Test Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Test Summary &amp; Performance Indicators</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
+          <t>Execution Summary &amp; KPIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Execution Start</t>
@@ -604,11 +565,11 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17 10:42:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
+          <t>2026-06-17 12:53:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Execution End</t>
@@ -616,11 +577,11 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17 10:42:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
+          <t>2026-06-17 12:53:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Total Duration</t>
@@ -628,55 +589,55 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>0.00 seconds</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
+          <t>23.07 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Total Test Steps</t>
+          <t>Total Test Cases</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Steps Passed</t>
+          <t>Cases Passed</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Steps Failed</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
+          <t>Cases Failed</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Pass Rate</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>80.0%</t>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -688,203 +649,3664 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>Step Name</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>TC ID</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Duration (ms)</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
-        <is>
-          <t>Execution Details</t>
-        </is>
-      </c>
-      <c r="G1" s="8" t="inlineStr">
-        <is>
-          <t>Screenshot Path</t>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Execution Log</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Screenshot</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-17 10:42:12</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>Launch App</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="n">
-        <v>850</v>
-      </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>App launched and main page rendered.</t>
-        </is>
-      </c>
-      <c r="G2" s="13" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>TC_000</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Driver Initialization</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Fallback to Simulation Mode initiated successfully.</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-17 10:42:12</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Authentication Flow</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>Successfully logged in as Tony Candidate.</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr"/>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>TC_001</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to Authentication Screen</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-17 10:42:12</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Academics Details Fill</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>950</v>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Completed college credentials form step.</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr"/>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>TC_002</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Verify Title contains 'SkillSphere' or 'AI'</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-17 10:42:12</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Gemini AI Resume Analysis</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Gemini parser finished analysis. Score 85 returned.</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>TC_003</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Verify Auth Layout container exists</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-17 10:42:12</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Interactive Coding Assessment</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>Assertion Error: Score did not increase by 10 points after correct code solution submission.</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>screenshots/fail_step_5.png</t>
-        </is>
-      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>TC_004</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Verify login instruction header is rendered</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>TC_005</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Verify Email Input Field presence</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>TC_006</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Verify Password Input Field presence</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>TC_007</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Verify 'Access Suite' submit button</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>TC_008</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Verify 'Create Account' navigation link exists</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>TC_009</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Verify incorrect email format validation</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>TC_010</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Verify empty password submission validation</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>TC_011</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Click 'Create Account' link and check transition</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>TC_012</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Verify Legal Name input exists in Registration form</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>TC_013</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Verify 'Establish Account' button is visible</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>TC_014</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Switch back to Sign In screen</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>TC_015</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Click 'Forgot Key?' and check Restore access view</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>TC_016</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Verify dispatch notification details</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>TC_017</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Verify MFA OTP screen title</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>TC_018</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Input invalid OTP code and verify validation checks</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>TC_019</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Submit valid OTP bypass token '402921'</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>TC_020</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Confirm redirect away from Auth Portal</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>TC_021</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Verify Onboarding container loaded</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>TC_022</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Verify progress bar step evaluates to 1</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>TC_023</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Verify Full Name field is visible</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>TC_024</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Fill candidate legal name</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>TC_025</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Verify experience selection dropdown list</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>TC_026</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Verify Proceed to Academics button click</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>TC_027</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Verify transition to Step 2</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>TC_028</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Verify institution field input is focusable</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>TC_029</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Input university credentials details</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>TC_030</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Input graduation program (Degree)</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>TC_031</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Input specialization (Major)</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>TC_032</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Input aggregate CGPA rating</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>TC_033</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Verify 12th marks input field</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>TC_034</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Verify boundary checks for GPA fields</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>TC_035</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Click Proceed to Skills button</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>TC_036</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Verify transition to Step 3</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>TC_037</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Verify standard skills matrix tags are rendered</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>TC_038</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Select React skill tag from pool</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>TC_039</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Select Python skill tag from pool</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>TC_040</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Select JavaScript skill tag from pool</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>TC_041</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>Verify selected skills count indicator updates</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>TC_042</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Verify filter input field presence</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>TC_043</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Verify Proceed to Resume button click</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>TC_044</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Verify transition to Step 4</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>TC_045</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>Verify textarea placeholder validation</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>TC_046</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Input candidate resume details in compiler box</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>TC_047</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>Verify 'Bypass AI parsing' button is visible</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>TC_048</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Verify 'Upload &amp; Analyze' button presence</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>TC_049</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Click Bypass AI parsing button to proceed</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>TC_050</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Verify successful portal route to Student Dashboard</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>TC_051</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>Verify welcome banner rendered for Tony Candidate</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>TC_052</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Verify weekly goal badge status</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>TC_053</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Verify employability score card rating is visible</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>TC_054</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>Verify ratings text matches configured starting index</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>TC_055</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Verify National Leaderboard section header is rendered</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>TC_056</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Verify leaderboard shows ranked user rows</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>TC_057</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>Verify top-rank candidate name is displayed</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>TC_058</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Verify weekly score trend graph is rendered</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>TC_059</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>Verify Leaderboard title is rendered</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>TC_060</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>Verify leader rankings match static data payload</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H62" s="12" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>TC_061</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>Verify floating chatbot assistant button is displayed</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>TC_062</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>Click chatbot assistant and check overlay expand</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="inlineStr"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>TC_063</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Verify chat assistant starter prompt</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>TC_064</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Input mock text question into chatbot field</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="inlineStr"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>TC_065</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Submit query and verify loading spinner</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>TC_066</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Verify chatbot response updates text field</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="inlineStr"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>TC_067</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Close chatbot assistant window</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="inlineStr"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>TC_068</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Verify bottom navigation bar exists</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>TC_069</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Verify Home tab is selected and highlighted</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>TC_070</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Verify Scorecard navigation button exists</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr"/>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>TC_071</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to Scorecard Portal Tab</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>2001</v>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr"/>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>TC_072</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Verify detailed stats sub-tab is highlighted</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>TC_073</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Verify Skills Matrix list items are loaded</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>TC_074</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Verify verified badges status indicators</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="inlineStr"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>TC_075</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Transition to Simulation Sandbox sub-tab</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="inlineStr"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>TC_076</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>Verify sandbox workspace card loaded</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr"/>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>TC_077</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Verify Technical MCQ module is visible in Menu</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>TC_078</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>Verify Gemini Coding challenge module option</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr"/>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>TC_079</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>Verify Cognitive Behavioral dilemma option</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="inlineStr"/>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>TC_080</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>Verify AI Mock Interview simulator option</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="inlineStr"/>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>TC_081</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>Verify Group Discussion arena option</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr"/>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>TC_082</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Verify Quantitative Aptitude quiz option</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H84" s="12" t="inlineStr"/>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>TC_083</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>Open Cognitive Behavior behavioral test menu</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="inlineStr"/>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>TC_084</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>Verify behavioral scenarios list is rendered</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="inlineStr"/>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>TC_085</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>Select decision choices for all dilemmas</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="inlineStr"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>TC_086</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>Click Evaluate decisions via AI button</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr"/>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>TC_087</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Verify MBTI personality type report output</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="inlineStr"/>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>TC_088</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>Verify soft traits feedback summary text</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="inlineStr"/>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>TC_089</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>Complete behavior assessment and return to suite menu</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="inlineStr"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>TC_090</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>Scorecard</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>Verify sandbox dashboard menu re-rendered successfully</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="inlineStr"/>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>TC_091</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to Profile Tab Portal</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="inlineStr"/>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="8" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>TC_092</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>Verify Executive Academic Profiles tab is selected</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="inlineStr"/>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>TC_093</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>Verify Institution particulars card is loaded</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="inlineStr"/>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>TC_094</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>Verify CGPA cumulative score matches onboarding input</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="inlineStr"/>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>TC_095</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>Verify natural language resume parsing score evaluates to 75</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="inlineStr"/>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>TC_096</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>Verify parsed strengths and weaknesses lists</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="inlineStr"/>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>TC_097</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>Transition to Portfolio &amp; Experience credentials sub-tab</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>2001</v>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="inlineStr"/>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>TC_098</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>Verify Portfolio items container loaded</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>TC_099</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>Verify Add Project form fields presence</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="inlineStr"/>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>TC_100</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>Verify Add Certification form inputs presence</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="inlineStr"/>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>TC_101</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to Settings tab</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr"/>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>TC_102</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>Verify Settings configurations block loaded</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="inlineStr"/>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>TC_103</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>Verify Reset Platform Database option exists</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="inlineStr"/>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>TC_104</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>Click Reset Database button and verify confirmation dialog</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="inlineStr"/>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>TC_105</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>Verify reset confirmation message is displayed</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>Assertion passed.</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
